--- a/data/trans_dic/P74B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,5</t>
+          <t>0,0; 16,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,73</t>
+          <t>0,0; 38,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,77</t>
+          <t>0,0; 60,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,66</t>
+          <t>0,0; 44,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,73</t>
+          <t>0,0; 17,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,46</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,22</t>
+          <t>2,31; 23,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 21,57</t>
+          <t>2,1; 19,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,59</t>
+          <t>0,55; 6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,7</t>
+          <t>1,95; 8,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 36,69</t>
+          <t>16,07; 36,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 27,2</t>
+          <t>6,48; 27,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,3</t>
+          <t>0,51; 5,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 15,17</t>
+          <t>6,11; 14,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,68</t>
+          <t>4,13; 11,26</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,74</t>
+          <t>2,09; 6,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,57</t>
+          <t>2,29; 8,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 44,56</t>
+          <t>18,0; 45,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 25,71</t>
+          <t>11,87; 26,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 28,91</t>
+          <t>13,05; 27,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,85</t>
+          <t>2,72; 7,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,46</t>
+          <t>5,78; 11,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,36</t>
+          <t>6,51; 12,79</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,64</t>
+          <t>0,86; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,48</t>
+          <t>1,72; 6,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,94</t>
+          <t>2,72; 8,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,74; 81,57</t>
+          <t>59,42; 81,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,62; 52,99</t>
+          <t>34,53; 52,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 35,87</t>
+          <t>21,3; 37,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,52</t>
+          <t>11,8; 19,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 20,84</t>
+          <t>13,32; 21,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,94</t>
+          <t>9,65; 16,71</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,93</t>
+          <t>5,27; 11,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,43</t>
+          <t>5,53; 13,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 13,17</t>
+          <t>5,53; 12,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,98; 92,06</t>
+          <t>81,68; 92,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>80,01; 89,3</t>
+          <t>79,32; 88,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,82; 86,52</t>
+          <t>74,42; 86,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,37; 42,87</t>
+          <t>33,89; 42,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>38,78; 47,81</t>
+          <t>39,19; 48,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,83; 45,7</t>
+          <t>35,76; 44,75</t>
         </is>
       </c>
     </row>
@@ -1228,27 +1228,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,32; 24,44</t>
+          <t>14,31; 24,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,27; 35,07</t>
+          <t>22,79; 34,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 33,39</t>
+          <t>22,69; 34,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,42; 98,12</t>
+          <t>92,36; 98,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,48; 98,53</t>
+          <t>92,17; 98,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,28; 58,31</t>
+          <t>49,14; 58,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,95; 63,62</t>
+          <t>54,25; 64,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57,36; 66,16</t>
+          <t>57,42; 66,14</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 26,32</t>
+          <t>13,32; 26,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,38; 43,72</t>
+          <t>28,26; 44,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,44; 36,57</t>
+          <t>23,02; 36,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88,54; 98,93</t>
+          <t>87,53; 98,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,47; 100,0</t>
+          <t>96,16; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66; 100,0</t>
+          <t>93,8; 100,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,91; 58,95</t>
+          <t>46,11; 58,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58,57; 70,24</t>
+          <t>59,27; 70,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,92; 67,67</t>
+          <t>56,59; 67,75</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,08</t>
+          <t>6,17; 9,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,6</t>
+          <t>10,81; 14,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,32</t>
+          <t>10,83; 14,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79,79; 85,74</t>
+          <t>79,66; 85,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,75; 70,87</t>
+          <t>64,87; 71,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,64; 69,35</t>
+          <t>62,96; 69,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,26</t>
+          <t>28,29; 32,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,72; 36,83</t>
+          <t>32,85; 36,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,87; 36,1</t>
+          <t>31,98; 35,98</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1967</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 4201</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8843</t>
+          <t>0; 8879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3857</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7877</t>
+          <t>0; 7871</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5500</t>
+          <t>0; 5581</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4232</t>
+          <t>0; 5103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1000; 8994</t>
+          <t>981; 10144</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1715; 11617</t>
+          <t>1130; 10637</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>935; 9378</t>
+          <t>922; 10271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5123</t>
+          <t>0; 4869</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3044; 15303</t>
+          <t>3082; 13857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1697</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12960; 29806</t>
+          <t>13060; 29429</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2943; 13779</t>
+          <t>3282; 13724</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>925; 9559</t>
+          <t>921; 10007</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12896; 33066</t>
+          <t>13316; 32050</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8902; 24345</t>
+          <t>8613; 23466</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6429</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5706; 18014</t>
+          <t>5587; 18369</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5708; 21416</t>
+          <t>5723; 19995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8098; 20751</t>
+          <t>8384; 20968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15005; 31369</t>
+          <t>14484; 32294</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14015; 31824</t>
+          <t>14372; 30512</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8731; 24171</t>
+          <t>8374; 23648</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23097; 44631</t>
+          <t>22492; 43882</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22254; 44517</t>
+          <t>23446; 46059</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2648; 13485</t>
+          <t>2507; 12456</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4962; 17433</t>
+          <t>4615; 17050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7786; 23898</t>
+          <t>7282; 23033</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42231; 56715</t>
+          <t>41316; 56770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45959; 70354</t>
+          <t>45843; 69891</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28811; 49429</t>
+          <t>29360; 51271</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43121; 70256</t>
+          <t>42495; 71097</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52237; 83702</t>
+          <t>53508; 86520</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40558; 68662</t>
+          <t>39089; 67709</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14823; 33300</t>
+          <t>14713; 33465</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15168; 37199</t>
+          <t>15322; 36926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14991; 35359</t>
+          <t>14856; 34829</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137902; 154856</t>
+          <t>137398; 154797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>183127; 204380</t>
+          <t>181543; 203450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>156327; 180785</t>
+          <t>155496; 180841</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>149235; 191719</t>
+          <t>151595; 191645</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>196171; 241823</t>
+          <t>198221; 242870</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>171077; 218186</t>
+          <t>170746; 213653</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34625; 59100</t>
+          <t>34592; 58344</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52099; 82048</t>
+          <t>53311; 81858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52688; 79739</t>
+          <t>54179; 81351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>183472; 194778</t>
+          <t>183346; 194716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>179377; 191093</t>
+          <t>178761; 191079</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>210641; 217721</t>
+          <t>210655; 217721</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>216993; 256737</t>
+          <t>216372; 255653</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>230849; 272226</t>
+          <t>232136; 274117</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>261857; 302030</t>
+          <t>262114; 301939</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18859; 37132</t>
+          <t>18789; 37663</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47349; 72927</t>
+          <t>47139; 73458</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35758; 55783</t>
+          <t>35111; 55244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97589; 109035</t>
+          <t>96476; 109006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>135759; 142194</t>
+          <t>136735; 142194</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>132665; 140151</t>
+          <t>131455; 140151</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>115376; 148140</t>
+          <t>115867; 146875</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>180997; 217057</t>
+          <t>183147; 217655</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166581; 198043</t>
+          <t>165618; 198284</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87757; 128470</t>
+          <t>87341; 128270</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>148641; 200744</t>
+          <t>148660; 199512</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>145447; 194464</t>
+          <t>147024; 194003</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>488369; 524803</t>
+          <t>487602; 524709</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>594825; 651059</t>
+          <t>595942; 654384</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>561515; 621681</t>
+          <t>564336; 621389</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>574679; 654034</t>
+          <t>573623; 658317</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>750687; 845000</t>
+          <t>753662; 847521</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>718371; 813686</t>
+          <t>720959; 811145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P74B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Edad-trans_dic.xlsx
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,98</t>
+          <t>0,0; 16,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,89</t>
+          <t>0,0; 39,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,96</t>
+          <t>0,0; 52,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,62</t>
+          <t>0,0; 46,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,99</t>
+          <t>0,0; 16,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 23,94</t>
+          <t>2,33; 22,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,75</t>
+          <t>2,12; 20,03</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,12</t>
+          <t>0,55; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,79</t>
+          <t>2,14; 9,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 36,22</t>
+          <t>15,9; 37,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 27,1</t>
+          <t>6,55; 27,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,55</t>
+          <t>0,52; 5,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 14,7</t>
+          <t>6,11; 14,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,26</t>
+          <t>3,96; 11,64</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,87</t>
+          <t>2,19; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,0</t>
+          <t>2,29; 8,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 45,03</t>
+          <t>18,11; 44,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 26,46</t>
+          <t>11,98; 25,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,05; 27,71</t>
+          <t>13,1; 28,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,68</t>
+          <t>2,68; 7,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,27</t>
+          <t>5,78; 11,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 12,79</t>
+          <t>6,6; 13,01</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,29</t>
+          <t>0,86; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,34</t>
+          <t>1,78; 6,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,61</t>
+          <t>3,05; 8,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,42; 81,65</t>
+          <t>59,27; 81,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,53; 52,64</t>
+          <t>34,58; 53,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 37,2</t>
+          <t>20,75; 36,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,75</t>
+          <t>12,27; 19,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 21,54</t>
+          <t>13,17; 21,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 16,71</t>
+          <t>9,92; 16,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,99</t>
+          <t>5,53; 12,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 13,33</t>
+          <t>5,87; 13,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 12,97</t>
+          <t>5,48; 12,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,68; 92,03</t>
+          <t>81,61; 91,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,32; 88,89</t>
+          <t>79,46; 89,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,42; 86,55</t>
+          <t>73,8; 86,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 42,85</t>
+          <t>33,3; 42,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,19; 48,02</t>
+          <t>38,53; 47,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,76; 44,75</t>
+          <t>35,82; 45,16</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,13</t>
+          <t>14,37; 24,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,79; 34,99</t>
+          <t>22,33; 34,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,69; 34,07</t>
+          <t>22,56; 33,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,36; 98,09</t>
+          <t>92,64; 98,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,17; 98,52</t>
+          <t>92,54; 98,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96,75; 100,0</t>
+          <t>97,18; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,14; 58,06</t>
+          <t>49,23; 58,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54,25; 64,06</t>
+          <t>54,69; 63,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57,42; 66,14</t>
+          <t>57,4; 66,23</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,32; 26,69</t>
+          <t>13,57; 26,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,26; 44,03</t>
+          <t>27,93; 44,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,02; 36,22</t>
+          <t>22,77; 35,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87,53; 98,9</t>
+          <t>88,2; 98,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,16; 100,0</t>
+          <t>96,2; 100,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,8; 100,0</t>
+          <t>93,83; 100,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,11; 58,44</t>
+          <t>46,6; 58,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>59,27; 70,44</t>
+          <t>58,99; 70,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>56,59; 67,75</t>
+          <t>56,47; 67,77</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,06</t>
+          <t>6,25; 9,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,51</t>
+          <t>10,75; 14,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,29</t>
+          <t>10,76; 14,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79,66; 85,73</t>
+          <t>79,55; 85,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,87; 71,23</t>
+          <t>64,96; 71,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,96; 69,32</t>
+          <t>62,85; 69,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,29; 32,47</t>
+          <t>28,27; 32,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,94</t>
+          <t>32,8; 36,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,98; 35,98</t>
+          <t>31,73; 35,65</t>
         </is>
       </c>
     </row>
@@ -1755,42 +1755,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8879</t>
+          <t>0; 8948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3934</t>
+          <t>0; 3384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7871</t>
+          <t>0; 8180</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5581</t>
+          <t>0; 5252</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5103</t>
+          <t>0; 5211</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>981; 10144</t>
+          <t>987; 9343</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1130; 10637</t>
+          <t>1142; 10786</t>
         </is>
       </c>
     </row>
@@ -1913,17 +1913,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>922; 10271</t>
+          <t>926; 9827</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 5011</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3082; 13857</t>
+          <t>3370; 14837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1933,27 +1933,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13060; 29429</t>
+          <t>12918; 30359</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3282; 13724</t>
+          <t>3317; 14139</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>921; 10007</t>
+          <t>935; 10470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13316; 32050</t>
+          <t>13314; 32298</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8613; 23466</t>
+          <t>8250; 24248</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 5660</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5587; 18369</t>
+          <t>5859; 18280</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5723; 19995</t>
+          <t>5731; 21092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8384; 20968</t>
+          <t>8433; 20764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14484; 32294</t>
+          <t>14622; 31517</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14372; 30512</t>
+          <t>14425; 31564</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8374; 23648</t>
+          <t>8254; 23945</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22492; 43882</t>
+          <t>22524; 44919</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23446; 46059</t>
+          <t>23766; 46845</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2507; 12456</t>
+          <t>2494; 13655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4615; 17050</t>
+          <t>4782; 18128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7282; 23033</t>
+          <t>8152; 24005</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41316; 56770</t>
+          <t>41209; 56731</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45843; 69891</t>
+          <t>45915; 71051</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29360; 51271</t>
+          <t>28592; 50620</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42495; 71097</t>
+          <t>44187; 71406</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53508; 86520</t>
+          <t>52908; 85248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39089; 67709</t>
+          <t>40221; 68191</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14713; 33465</t>
+          <t>15433; 34854</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15322; 36926</t>
+          <t>16248; 36815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14856; 34829</t>
+          <t>14721; 34662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137398; 154797</t>
+          <t>137280; 154655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>181543; 203450</t>
+          <t>181854; 205001</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>155496; 180841</t>
+          <t>154206; 181358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>151595; 191645</t>
+          <t>148951; 191863</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>198221; 242870</t>
+          <t>194871; 241032</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>170746; 213653</t>
+          <t>171039; 215633</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34592; 58344</t>
+          <t>34755; 59308</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53311; 81858</t>
+          <t>52240; 81453</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54179; 81351</t>
+          <t>53875; 79649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>183346; 194716</t>
+          <t>183914; 194889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>178761; 191079</t>
+          <t>179484; 190980</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>210655; 217721</t>
+          <t>211578; 217721</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>216372; 255653</t>
+          <t>216759; 255556</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>232136; 274117</t>
+          <t>234029; 273304</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>262114; 301939</t>
+          <t>262024; 302328</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18789; 37663</t>
+          <t>19142; 37969</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47139; 73458</t>
+          <t>46596; 74082</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35111; 55244</t>
+          <t>34726; 54781</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96476; 109006</t>
+          <t>97210; 109005</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>136735; 142194</t>
+          <t>136787; 142194</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>131455; 140151</t>
+          <t>131505; 140151</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>115867; 146875</t>
+          <t>117099; 147841</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>183147; 217655</t>
+          <t>182277; 217445</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>165618; 198284</t>
+          <t>165262; 198357</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87341; 128270</t>
+          <t>88479; 128871</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>148660; 199512</t>
+          <t>147863; 200353</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147024; 194003</t>
+          <t>146154; 195350</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>487602; 524709</t>
+          <t>486902; 525540</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>595942; 654384</t>
+          <t>596811; 652904</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>564336; 621389</t>
+          <t>563374; 623986</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>573623; 658317</t>
+          <t>573265; 654471</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>753662; 847521</t>
+          <t>752333; 845417</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>720959; 811145</t>
+          <t>715239; 803734</t>
         </is>
       </c>
     </row>
